--- a/セリフ編集/ナレーション・記事/新聞見出し系.xlsx
+++ b/セリフ編集/ナレーション・記事/新聞見出し系.xlsx
@@ -12883,11 +12883,6 @@
           <t xml:space="preserve">normal[1]</t>
         </is>
       </c>
-      <c r="F469" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
       <c r="G469" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">${d.winner.name}がメインイベントを制す</t>
@@ -12915,11 +12910,6 @@
           <t xml:space="preserve">normal[2]</t>
         </is>
       </c>
-      <c r="F470" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
       <c r="G470" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">${d.winner.name}、${d.finishLabel}で勝利</t>
@@ -12947,11 +12937,6 @@
           <t xml:space="preserve">normal[3]</t>
         </is>
       </c>
-      <c r="F471" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
       <c r="G471" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">${d.venue.name}のメイン、${d.winner.name}に軍配</t>
@@ -13357,11 +13342,6 @@
           <t xml:space="preserve">normal[1]</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
       <c r="G486" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">${d.venue.name}で行われた${d.showName}のメインイベントは、${d.winner.name}が${d.finishLabel}で${d.loser.name}を下して幕を閉じた。${d.turns}ターンの試合は${d.attendance.toLocaleString()}人の観客を沸かせ、MQ ${d.mq}を記録した。</t>
@@ -13387,11 +13367,6 @@
       <c r="D487" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">normal[2]</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G487" t="inlineStr" s="3">
